--- a/action_cop/output_excels/20_Promoter_Encumbrance_Details.xlsx
+++ b/action_cop/output_excels/20_Promoter_Encumbrance_Details.xlsx
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
@@ -1517,6 +1517,129 @@
       </c>
       <c r="Y10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/Disclosure1_10082026124603.zip</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08-Oct-2026 12:46:03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vodafone Idea Limited</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>30-Sep-2026 - 30-Sep-2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The encumbrance (non-disposal undertaking) has been created for the benefit of the Target Company</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>30-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>184675136</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>30-Sep-2026</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Creation</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>184675136</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     0.16</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>9801769868</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     0.87</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Asian Telecommunication Investments (Mauritius) Limited</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06-Oct-2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>43698</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>08-Oct-2026 12:46:06</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>00:00:03</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
